--- a/sample/sample_file_04_30_2026.xlsx
+++ b/sample/sample_file_04_30_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>sometypeofTextthatneeds to be serached</t>
   </si>
@@ -38,6 +38,21 @@
   </si>
   <si>
     <t>value3</t>
+  </si>
+  <si>
+    <t>Reporting dates</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>05/31/2026</t>
+  </si>
+  <si>
+    <t>04/30/2026</t>
   </si>
 </sst>
 </file>
@@ -348,6 +363,23 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
@@ -356,6 +388,12 @@
       <c r="C3" t="s">
         <v>2</v>
       </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -367,6 +405,12 @@
       <c r="C4" t="s">
         <v>3</v>
       </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -378,6 +422,9 @@
       <c r="C5" t="s">
         <v>7</v>
       </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
